--- a/health_insurance_data.xlsx
+++ b/health_insurance_data.xlsx
@@ -16,7 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +484,102 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PHOTO FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UJJJJJJU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UJHT4689</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4RF456</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>34567IU</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UHGJ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4567Y</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45673</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MONEY COLLECTION</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>uploads\WhatsApp Image 2025-01-15 at 5.43.09 AM.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IUJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HJKOI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>YTUYH</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FTRYTYREER</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>79865TGB</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45RTYH</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>45673</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PACKAGE UPCODING</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>uploads\WhatsApp Image 2025-01-15 at 5.43.09 AM.jpeg</t>
         </is>
       </c>
     </row>
